--- a/practice/answers/s1_q02.xlsx
+++ b/practice/answers/s1_q02.xlsx
@@ -501,7 +501,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Q2 — Three crops, one formula</t>
+          <t>Three crops, one formula</t>
         </is>
       </c>
     </row>

--- a/practice/answers/s1_q02.xlsx
+++ b/practice/answers/s1_q02.xlsx
@@ -569,7 +569,7 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Willow</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
@@ -597,7 +597,7 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
@@ -625,7 +625,7 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Creek</t>
+          <t>Slough</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
@@ -653,7 +653,7 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Quarter</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
@@ -681,7 +681,7 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Rented</t>
+          <t>Airport</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">

--- a/practice/answers/s1_q02.xlsx
+++ b/practice/answers/s1_q02.xlsx
@@ -1,87 +1,147 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59976752FD9C6150914790562C903547A1E0B8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{508BA356-F3EB-465D-9794-90B913456102}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Answer" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+  <si>
+    <t>Three crops, one formula</t>
+  </si>
+  <si>
+    <t>Prices run across row 4; yields run down. A single formula fills the whole revenue block: the price row is locked with B$4, the yield column is not.</t>
+  </si>
+  <si>
+    <t>Price ($/bu)</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Canola</t>
+  </si>
+  <si>
+    <t>Wheat</t>
+  </si>
+  <si>
+    <t>Barley</t>
+  </si>
+  <si>
+    <t>Willow</t>
+  </si>
+  <si>
+    <t>Ridge</t>
+  </si>
+  <si>
+    <t>Slough</t>
+  </si>
+  <si>
+    <t>Quarter</t>
+  </si>
+  <si>
+    <t>Airport</t>
+  </si>
+  <si>
+    <t>One formula, =B6*B$4, fills all fifteen cells. Only the price ROW is locked; the column moves so each crop meets its own price.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="8">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FF4A7C59"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="13"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF5C6B62"/>
       <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF24302A"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF24302A"/>
       <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF2F5D46"/>
       <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF5C6B62"/>
       <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="FFF6EFD9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="FF4A7C59"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,102 +157,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -480,247 +482,222 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="3" customWidth="1"/>
+    <col min="6" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Three crops, one formula</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Prices run across row 4; yields run down. A single formula fills the whole revenue block: the price row is locked with B$4, the yield column is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Price ($/bu)</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
+    <row r="1" spans="1:8" ht="18" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="32.1" customHeight="1">
+      <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1"/>
+    <row r="4" spans="1:8" ht="18" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
         <v>14.2</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="3">
         <v>8.35</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="3">
         <v>5.6</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Canola</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Wheat</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Barley</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Canola</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Wheat</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Barley</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Willow</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
+    <row r="5" spans="1:8" ht="18" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1">
+      <c r="A6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="7">
         <v>41.2</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="7">
         <v>52.4</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="7">
         <v>63.1</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <f>B6*B$4</f>
-        <v/>
-      </c>
-      <c r="G6" s="9">
+        <v>585.04</v>
+      </c>
+      <c r="G6" s="8">
         <f>C6*C$4</f>
-        <v/>
-      </c>
-      <c r="H6" s="9">
+        <v>437.53999999999996</v>
+      </c>
+      <c r="H6" s="8">
         <f>D6*D$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
+        <v>353.36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18" customHeight="1">
+      <c r="A7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="7">
         <v>38.6</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="7">
         <v>49.8</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="7">
         <v>58.7</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <f>B7*B$4</f>
-        <v/>
-      </c>
-      <c r="G7" s="9">
+        <v>548.12</v>
+      </c>
+      <c r="G7" s="8">
         <f>C7*C$4</f>
-        <v/>
-      </c>
-      <c r="H7" s="9">
+        <v>415.83</v>
+      </c>
+      <c r="H7" s="8">
         <f>D7*D$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Slough</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
+        <v>328.71999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="7">
         <v>44.8</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="7">
         <v>55.2</v>
       </c>
-      <c r="D8" s="8" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="F8" s="9">
+      <c r="D8" s="7">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="F8" s="8">
         <f>B8*B$4</f>
-        <v/>
-      </c>
-      <c r="G8" s="9">
+        <v>636.16</v>
+      </c>
+      <c r="G8" s="8">
         <f>C8*C$4</f>
-        <v/>
-      </c>
-      <c r="H8" s="9">
+        <v>460.92</v>
+      </c>
+      <c r="H8" s="8">
         <f>D8*D$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Quarter</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
+        <v>371.84000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="7">
         <v>36.1</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="7">
         <v>47.3</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="7">
         <v>61.9</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <f>B9*B$4</f>
-        <v/>
-      </c>
-      <c r="G9" s="9">
+        <v>512.62</v>
+      </c>
+      <c r="G9" s="8">
         <f>C9*C$4</f>
-        <v/>
-      </c>
-      <c r="H9" s="9">
+        <v>394.95499999999998</v>
+      </c>
+      <c r="H9" s="8">
         <f>D9*D$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Airport</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
+        <v>346.64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18" customHeight="1">
+      <c r="A10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="7">
         <v>39.9</v>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C10" s="7">
         <v>51</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="7">
         <v>60.2</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="8">
         <f>B10*B$4</f>
-        <v/>
-      </c>
-      <c r="G10" s="9">
+        <v>566.57999999999993</v>
+      </c>
+      <c r="G10" s="8">
         <f>C10*C$4</f>
-        <v/>
-      </c>
-      <c r="H10" s="9">
+        <v>425.84999999999997</v>
+      </c>
+      <c r="H10" s="8">
         <f>D10*D$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="F11" s="10">
-        <f>_xlfn.FORMULATEXT(F6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1"/>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>One formula, =B6*B$4, fills all fifteen cells. Only the price ROW is locked; the column moves so each crop meets its own price.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1"/>
+        <v>337.12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18" customHeight="1">
+      <c r="F11" s="9" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(F6)</f>
+        <v>=B6*B$4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1"/>
+    <row r="13" spans="1:8" ht="30" customHeight="1">
+      <c r="A13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+    </row>
+    <row r="14" spans="1:8" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A13:H13"/>

--- a/practice/answers/s1_q02.xlsx
+++ b/practice/answers/s1_q02.xlsx
@@ -1,147 +1,67 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59976752FD9C6150914790562C903547A1E0B8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{508BA356-F3EB-465D-9794-90B913456102}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
-  <si>
-    <t>Three crops, one formula</t>
-  </si>
-  <si>
-    <t>Prices run across row 4; yields run down. A single formula fills the whole revenue block: the price row is locked with B$4, the yield column is not.</t>
-  </si>
-  <si>
-    <t>Price ($/bu)</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Canola</t>
-  </si>
-  <si>
-    <t>Wheat</t>
-  </si>
-  <si>
-    <t>Barley</t>
-  </si>
-  <si>
-    <t>Willow</t>
-  </si>
-  <si>
-    <t>Ridge</t>
-  </si>
-  <si>
-    <t>Slough</t>
-  </si>
-  <si>
-    <t>Quarter</t>
-  </si>
-  <si>
-    <t>Airport</t>
-  </si>
-  <si>
-    <t>One formula, =B6*B$4, fills all fifteen cells. Only the price ROW is locked; the column moves so each crop meets its own price.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color rgb="FF4A7C59"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF5C6B62"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF24302A"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF24302A"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF2F5D46"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF5C6B62"/>
-      <name val="Arial"/>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6EFD9"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4A7C59"/>
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -157,44 +77,102 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -482,226 +460,384 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="3" customWidth="1"/>
-    <col min="6" max="8" width="11" customWidth="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="32.1" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-    </row>
-    <row r="3" spans="1:8" ht="18" customHeight="1"/>
-    <row r="4" spans="1:8" ht="18" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Price ($/bu)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C1" s="2" t="n">
         <v>8.35</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D1" s="2" t="n">
         <v>5.6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1">
-      <c r="A6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="7">
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Canola</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Barley</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Revenue ($/ac)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Canola</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Barley</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
         <v>41.2</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C3" s="4" t="n">
         <v>52.4</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D3" s="4" t="n">
         <v>63.1</v>
       </c>
-      <c r="F6" s="8">
-        <f>B6*B$4</f>
-        <v>585.04</v>
-      </c>
-      <c r="G6" s="8">
-        <f>C6*C$4</f>
-        <v>437.53999999999996</v>
-      </c>
-      <c r="H6" s="8">
-        <f>D6*D$4</f>
-        <v>353.36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1">
-      <c r="A7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="7">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="G3" s="5">
+        <f>B3*B$1</f>
+        <v/>
+      </c>
+      <c r="H3" s="5">
+        <f>C3*C$1</f>
+        <v/>
+      </c>
+      <c r="I3" s="5">
+        <f>D3*D$1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
         <v>38.6</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C4" s="4" t="n">
         <v>49.8</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D4" s="4" t="n">
         <v>58.7</v>
       </c>
-      <c r="F7" s="8">
-        <f>B7*B$4</f>
-        <v>548.12</v>
-      </c>
-      <c r="G7" s="8">
-        <f>C7*C$4</f>
-        <v>415.83</v>
-      </c>
-      <c r="H7" s="8">
-        <f>D7*D$4</f>
-        <v>328.71999999999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="G4" s="5">
+        <f>B4*B$1</f>
+        <v/>
+      </c>
+      <c r="H4" s="5">
+        <f>C4*C$1</f>
+        <v/>
+      </c>
+      <c r="I4" s="5">
+        <f>D4*D$1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Creek</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
         <v>44.8</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C5" s="4" t="n">
         <v>55.2</v>
       </c>
-      <c r="D8" s="7">
-        <v>66.400000000000006</v>
-      </c>
-      <c r="F8" s="8">
-        <f>B8*B$4</f>
-        <v>636.16</v>
-      </c>
-      <c r="G8" s="8">
-        <f>C8*C$4</f>
-        <v>460.92</v>
-      </c>
-      <c r="H8" s="8">
-        <f>D8*D$4</f>
-        <v>371.84000000000003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="7">
+      <c r="D5" s="4" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Creek</t>
+        </is>
+      </c>
+      <c r="G5" s="5">
+        <f>B5*B$1</f>
+        <v/>
+      </c>
+      <c r="H5" s="5">
+        <f>C5*C$1</f>
+        <v/>
+      </c>
+      <c r="I5" s="5">
+        <f>D5*D$1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
         <v>36.1</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C6" s="4" t="n">
         <v>47.3</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D6" s="4" t="n">
         <v>61.9</v>
       </c>
-      <c r="F9" s="8">
-        <f>B9*B$4</f>
-        <v>512.62</v>
-      </c>
-      <c r="G9" s="8">
-        <f>C9*C$4</f>
-        <v>394.95499999999998</v>
-      </c>
-      <c r="H9" s="8">
-        <f>D9*D$4</f>
-        <v>346.64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1">
-      <c r="A10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="7">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="G6" s="5">
+        <f>B6*B$1</f>
+        <v/>
+      </c>
+      <c r="H6" s="5">
+        <f>C6*C$1</f>
+        <v/>
+      </c>
+      <c r="I6" s="5">
+        <f>D6*D$1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rented</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
         <v>39.9</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C7" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D7" s="4" t="n">
         <v>60.2</v>
       </c>
-      <c r="F10" s="8">
-        <f>B10*B$4</f>
-        <v>566.57999999999993</v>
-      </c>
-      <c r="G10" s="8">
-        <f>C10*C$4</f>
-        <v>425.84999999999997</v>
-      </c>
-      <c r="H10" s="8">
-        <f>D10*D$4</f>
-        <v>337.12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1">
-      <c r="F11" s="9" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(F6)</f>
-        <v>=B6*B$4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1"/>
-    <row r="13" spans="1:8" ht="30" customHeight="1">
-      <c r="A13" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-    </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rented</t>
+        </is>
+      </c>
+      <c r="G7" s="5">
+        <f>B7*B$1</f>
+        <v/>
+      </c>
+      <c r="H7" s="5">
+        <f>C7*C$1</f>
+        <v/>
+      </c>
+      <c r="I7" s="5">
+        <f>D7*D$1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="G8" s="7">
+        <f>AVERAGE(G3:G7)</f>
+        <v/>
+      </c>
+      <c r="H8" s="7">
+        <f>AVERAGE(H3:H7)</f>
+        <v/>
+      </c>
+      <c r="I8" s="7">
+        <f>AVERAGE(I3:I7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Formula: =B3*B$1, filled across and down. The row of the price reference is locked (B$1); the column is not, so each crop meets its own price.</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Canola gives the highest average revenue per acre, by $142.69 over wheat.</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="11" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="11" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>With $B$1 every column would use the canola price, so wheat and barley revenues would be roughly 70% and 150% too high. The sheet would still fill with plausible dollar figures, so nothing would look broken.</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="13" t="n"/>
+      <c r="I14" s="13" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="13" t="n"/>
+      <c r="I15" s="13" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Part (e)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A2:H2"/>
+  <mergeCells count="3">
+    <mergeCell ref="A14:I15"/>
+    <mergeCell ref="A10:I11"/>
+    <mergeCell ref="A12:I13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q02.xlsx
+++ b/practice/answers/s1_q02.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -46,7 +45,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE2F3"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -56,7 +55,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00CFE2F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -77,29 +76,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,379 +460,298 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Price ($/bu)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="C1" s="2" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="D1" s="2" t="n">
-        <v>5.6</v>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Canola</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Barley</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Rev Canola ($/ac)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Rev Wheat ($/ac)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Rev Barley ($/ac)</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Canola</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>Wheat</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Barley</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Revenue ($/ac)</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Canola</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Wheat</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>Barley</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="F2" s="2">
+        <f>B2*B$8</f>
+        <v/>
+      </c>
+      <c r="G2" s="2">
+        <f>C2*C$8</f>
+        <v/>
+      </c>
+      <c r="H2" s="2">
+        <f>D2*D$8</f>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>63.1</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="G3" s="5">
-        <f>B3*B$1</f>
-        <v/>
-      </c>
-      <c r="H3" s="5">
-        <f>C3*C$1</f>
-        <v/>
-      </c>
-      <c r="I3" s="5">
-        <f>D3*D$1</f>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="C3" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="F3" s="2">
+        <f>B3*B$8</f>
+        <v/>
+      </c>
+      <c r="G3" s="2">
+        <f>C3*C$8</f>
+        <v/>
+      </c>
+      <c r="H3" s="2">
+        <f>D3*D$8</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="G4" s="5">
-        <f>B4*B$1</f>
-        <v/>
-      </c>
-      <c r="H4" s="5">
-        <f>C4*C$1</f>
-        <v/>
-      </c>
-      <c r="I4" s="5">
-        <f>D4*D$1</f>
+          <t>Creek</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="F4" s="2">
+        <f>B4*B$8</f>
+        <v/>
+      </c>
+      <c r="G4" s="2">
+        <f>C4*C$8</f>
+        <v/>
+      </c>
+      <c r="H4" s="2">
+        <f>D4*D$8</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Creek</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Creek</t>
-        </is>
-      </c>
-      <c r="G5" s="5">
-        <f>B5*B$1</f>
-        <v/>
-      </c>
-      <c r="H5" s="5">
-        <f>C5*C$1</f>
-        <v/>
-      </c>
-      <c r="I5" s="5">
-        <f>D5*D$1</f>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="F5" s="2">
+        <f>B5*B$8</f>
+        <v/>
+      </c>
+      <c r="G5" s="2">
+        <f>C5*C$8</f>
+        <v/>
+      </c>
+      <c r="H5" s="2">
+        <f>D5*D$8</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="G6" s="5">
-        <f>B6*B$1</f>
-        <v/>
-      </c>
-      <c r="H6" s="5">
-        <f>C6*C$1</f>
-        <v/>
-      </c>
-      <c r="I6" s="5">
-        <f>D6*D$1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
           <t>Rented</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B6" t="n">
         <v>39.9</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C6" t="n">
         <v>51</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D6" t="n">
         <v>60.2</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Rented</t>
-        </is>
-      </c>
-      <c r="G7" s="5">
-        <f>B7*B$1</f>
-        <v/>
-      </c>
-      <c r="H7" s="5">
-        <f>C7*C$1</f>
-        <v/>
-      </c>
-      <c r="I7" s="5">
-        <f>D7*D$1</f>
+      <c r="F6" s="2">
+        <f>B6*B$8</f>
+        <v/>
+      </c>
+      <c r="G6" s="2">
+        <f>C6*C$8</f>
+        <v/>
+      </c>
+      <c r="H6" s="2">
+        <f>D6*D$8</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="G8" s="7">
-        <f>AVERAGE(G3:G7)</f>
-        <v/>
-      </c>
-      <c r="H8" s="7">
-        <f>AVERAGE(H3:H7)</f>
-        <v/>
-      </c>
-      <c r="I8" s="7">
-        <f>AVERAGE(I3:I7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Formula: =B3*B$1, filled across and down. The row of the price reference is locked (B$1); the column is not, so each crop meets its own price.</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="9" t="n"/>
-      <c r="I10" s="9" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="n"/>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Canola gives the highest average revenue per acre, by $142.69 over wheat.</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>With $B$1 every column would use the canola price, so wheat and barley revenues would be roughly 70% and 150% too high. The sheet would still fill with plausible dollar figures, so nothing would look broken.</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="13" t="n"/>
-      <c r="H14" s="13" t="n"/>
-      <c r="I14" s="13" t="n"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Price ($/bu)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Average (d):</t>
+        </is>
+      </c>
+      <c r="F9" s="3">
+        <f>AVERAGE(F2:F6)</f>
+        <v/>
+      </c>
+      <c r="G9" s="3">
+        <f>AVERAGE(G2:G6)</f>
+        <v/>
+      </c>
+      <c r="H9" s="3">
+        <f>AVERAGE(H2:H6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>(b) Top-left formula: =B2*B$8. The row of the price reference is locked (the 8), so filling down keeps pointing at the price row; the column is left free, so filling across moves from the canola price to the wheat and barley prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>(c) With a fully absolute reference like $B$8, every copy of the formula would multiply by the canola price -- the wheat and barley revenue columns would silently be wrong, and Excel would show no error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>(e) Canola earns the highest average revenue per acre, about $570/ac -- roughly $143/ac more than wheat (about $427/ac), with barley third (about $348/ac).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="n"/>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="13" t="n"/>
-      <c r="H15" s="13" t="n"/>
-      <c r="I15" s="13" t="n"/>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Legend: colours mark question parts</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>Part (a)</t>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Part (b)</t>
+          <t>Part (c)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Part (c)</t>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Part (d)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
           <t>Part (e)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A14:I15"/>
-    <mergeCell ref="A10:I11"/>
-    <mergeCell ref="A12:I13"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q02.xlsx
+++ b/practice/answers/s1_q02.xlsx
@@ -684,21 +684,21 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="64" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>(b) Top-left formula: =B2*B$8. The row of the price reference is locked (the 8), so filling down keeps pointing at the price row; the column is left free, so filling across moves from the canola price to the wheat and barley prices.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="64" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>(c) With a fully absolute reference like $B$8, every copy of the formula would multiply by the canola price -- the wheat and barley revenue columns would silently be wrong, and Excel would show no error.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="45" customHeight="1">
+    <row r="13" ht="64" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
           <t>(e) Canola earns the highest average revenue per acre, about $570/ac -- roughly $143/ac more than wheat (about $427/ac), with barley third (about $348/ac).</t>

--- a/practice/answers/s1_q02.xlsx
+++ b/practice/answers/s1_q02.xlsx
@@ -1,66 +1,158 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_884D9827905596AFE448FC555F7B8E3B851EEC8A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05A1834C-98D6-4321-A312-8190AAD250A5}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Answer" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Canola</t>
+  </si>
+  <si>
+    <t>Wheat</t>
+  </si>
+  <si>
+    <t>Barley</t>
+  </si>
+  <si>
+    <t>Rev Canola ($/ac)</t>
+  </si>
+  <si>
+    <t>Rev Wheat ($/ac)</t>
+  </si>
+  <si>
+    <t>Rev Barley ($/ac)</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>Creek</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Rented</t>
+  </si>
+  <si>
+    <t>Price ($/bu)</t>
+  </si>
+  <si>
+    <t>Average (d):</t>
+  </si>
+  <si>
+    <t>(b) Top-left formula: =B2*B$8. The row of the price reference is locked (the 8), so filling down keeps pointing at the price row; the column is left free, so filling across moves from the canola price to the wheat and barley prices.</t>
+  </si>
+  <si>
+    <t>(c) With a fully absolute reference like $B$8, every copy of the formula would multiply by the canola price -- the wheat and barley revenue columns would silently be wrong, and Excel would show no error.</t>
+  </si>
+  <si>
+    <t>(e) Canola earns the highest average revenue per acre, about $570/ac -- roughly $143/ac more than wheat (about $427/ac), with barley third (about $348/ac).</t>
+  </si>
+  <si>
+    <t>Legend: colours mark question parts</t>
+  </si>
+  <si>
+    <t>Part (a)</t>
+  </si>
+  <si>
+    <t>Part (b)</t>
+  </si>
+  <si>
+    <t>Part (c)</t>
+  </si>
+  <si>
+    <t>Part (d)</t>
+  </si>
+  <si>
+    <t>Part (e)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE2F3"/>
+        <fgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
+        <fgColor rgb="FFD9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,98 +168,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -455,296 +489,257 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="4" width="9" customWidth="1"/>
+    <col min="6" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Canola</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Wheat</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Barley</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Rev Canola ($/ac)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Rev Wheat ($/ac)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Rev Barley ($/ac)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
         <v>41.2</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>52.4</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>63.1</v>
       </c>
       <c r="F2" s="2">
         <f>B2*B$8</f>
-        <v/>
+        <v>585.04</v>
       </c>
       <c r="G2" s="2">
         <f>C2*C$8</f>
-        <v/>
+        <v>437.53999999999996</v>
       </c>
       <c r="H2" s="2">
         <f>D2*D$8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+        <v>353.36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
         <v>38.6</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>49.8</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>58.7</v>
       </c>
       <c r="F3" s="2">
         <f>B3*B$8</f>
-        <v/>
+        <v>548.12</v>
       </c>
       <c r="G3" s="2">
         <f>C3*C$8</f>
-        <v/>
+        <v>415.83</v>
       </c>
       <c r="H3" s="2">
         <f>D3*D$8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Creek</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+        <v>328.71999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
         <v>44.8</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>55.2</v>
       </c>
-      <c r="D4" t="n">
-        <v>66.40000000000001</v>
+      <c r="D4">
+        <v>66.400000000000006</v>
       </c>
       <c r="F4" s="2">
         <f>B4*B$8</f>
-        <v/>
+        <v>636.16</v>
       </c>
       <c r="G4" s="2">
         <f>C4*C$8</f>
-        <v/>
+        <v>460.92</v>
       </c>
       <c r="H4" s="2">
         <f>D4*D$8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+        <v>371.84000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
         <v>36.1</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>47.3</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>61.9</v>
       </c>
       <c r="F5" s="2">
         <f>B5*B$8</f>
-        <v/>
+        <v>512.62</v>
       </c>
       <c r="G5" s="2">
         <f>C5*C$8</f>
-        <v/>
+        <v>394.95499999999998</v>
       </c>
       <c r="H5" s="2">
         <f>D5*D$8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Rented</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+        <v>346.64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
         <v>39.9</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>51</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>60.2</v>
       </c>
       <c r="F6" s="2">
         <f>B6*B$8</f>
-        <v/>
+        <v>566.57999999999993</v>
       </c>
       <c r="G6" s="2">
         <f>C6*C$8</f>
-        <v/>
+        <v>425.84999999999997</v>
       </c>
       <c r="H6" s="2">
         <f>D6*D$8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Price ($/bu)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+        <v>337.12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
         <v>14.2</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>8.35</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>5.6</v>
       </c>
     </row>
-    <row r="9">
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>Average (d):</t>
-        </is>
+    <row r="9" spans="1:8">
+      <c r="E9" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F9" s="3">
         <f>AVERAGE(F2:F6)</f>
-        <v/>
+        <v>569.70399999999995</v>
       </c>
       <c r="G9" s="3">
         <f>AVERAGE(G2:G6)</f>
-        <v/>
+        <v>427.01899999999995</v>
       </c>
       <c r="H9" s="3">
         <f>AVERAGE(H2:H6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>(b) Top-left formula: =B2*B$8. The row of the price reference is locked (the 8), so filling down keeps pointing at the price row; the column is left free, so filling across moves from the canola price to the wheat and barley prices.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="64" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>(c) With a fully absolute reference like $B$8, every copy of the formula would multiply by the canola price -- the wheat and barley revenue columns would silently be wrong, and Excel would show no error.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="64" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>(e) Canola earns the highest average revenue per acre, about $570/ac -- roughly $143/ac more than wheat (about $427/ac), with barley third (about $348/ac).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Legend: colours mark question parts</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Part (a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Part (b)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Part (c)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Part (d)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Part (e)</t>
-        </is>
+        <v>347.53599999999994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="63.95" customHeight="1">
+      <c r="A11" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+    </row>
+    <row r="12" spans="1:8" ht="63.95" customHeight="1">
+      <c r="A12" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+    </row>
+    <row r="13" spans="1:8" ht="63.95" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="8" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
